--- a/evac_by_zip/evac_by_zip_2026-08-30.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-30.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 209 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 208 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -1248,11 +1248,11 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>97703</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1274,23 +1274,23 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Deschutes</t>
+          <t>Crook</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1312,23 +1312,23 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1350,19 +1350,19 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -1397,99 +1397,61 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>97058</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Placed on a ZIP code (table above)</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>861</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>823</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1730</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Placed on a ZIP code (table above)</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>926</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>823</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>1795</v>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Not placed on any ZIP code (unmatched)</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n">
+        <v>152</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>208</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Not placed on any ZIP code (unmatched)</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>153</v>
-      </c>
-      <c r="C28" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Reconciled total (matches morning report)</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
-        <v>1079</v>
-      </c>
-      <c r="C29" s="18" t="n">
+      <c r="B28" s="18" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C28" s="18" t="n">
         <v>850</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D28" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="E29" s="18" t="n">
-        <v>2004</v>
+      <c r="E28" s="18" t="n">
+        <v>1938</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6151,22 +6113,22 @@
     <row r="134">
       <c r="A134" s="25" t="inlineStr">
         <is>
-          <t>97703</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="B134" s="26" t="inlineStr">
         <is>
-          <t>US-OR-DES-BND-357</t>
+          <t>US-OR-CRO-CRR-8SB</t>
         </is>
       </c>
       <c r="C134" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D134" s="26" t="inlineStr">
         <is>
-          <t>Deschutes</t>
+          <t>Crook</t>
         </is>
       </c>
       <c r="E134" s="25" t="inlineStr">
@@ -6176,11 +6138,11 @@
       </c>
       <c r="F134" s="25" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="G134" s="25" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135">
@@ -6191,7 +6153,7 @@
       </c>
       <c r="B135" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SB</t>
+          <t>US-OR-CRO-CRR-4SC</t>
         </is>
       </c>
       <c r="C135" s="26" t="inlineStr">
@@ -6211,11 +6173,11 @@
       </c>
       <c r="F135" s="25" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G135" s="25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
@@ -6226,7 +6188,7 @@
       </c>
       <c r="B136" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC</t>
+          <t>US-OR-CRO-CRR-4SK-A</t>
         </is>
       </c>
       <c r="C136" s="26" t="inlineStr">
@@ -6250,28 +6212,28 @@
         </is>
       </c>
       <c r="G136" s="25" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="25" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>97603</t>
         </is>
       </c>
       <c r="B137" s="26" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-A</t>
+          <t>US-OR-KLA-KLA-1941</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D137" s="26" t="inlineStr">
         <is>
-          <t>Crook</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -6281,32 +6243,32 @@
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G137" s="25" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="25" t="inlineStr">
         <is>
-          <t>97603</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="B138" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1941</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C138" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D138" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
@@ -6316,22 +6278,22 @@
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="G138" s="25" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="25" t="inlineStr">
         <is>
-          <t>97037</t>
+          <t>97058</t>
         </is>
       </c>
       <c r="B139" s="26" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="C139" s="26" t="inlineStr">
@@ -6351,7 +6313,7 @@
       </c>
       <c r="F139" s="25" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G139" s="25" t="n">
@@ -6361,12 +6323,12 @@
     <row r="140">
       <c r="A140" s="25" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B140" s="26" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C140" s="26" t="inlineStr">
@@ -6376,7 +6338,7 @@
       </c>
       <c r="D140" s="26" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E140" s="25" t="inlineStr">
@@ -6386,50 +6348,15 @@
       </c>
       <c r="F140" s="25" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G140" s="25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B141" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C141" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D141" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E141" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F141" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G141" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" s="27" t="inlineStr">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -6437,7 +6364,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A143:G143"/>
+    <mergeCell ref="A142:G142"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
